--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,15 +434,25 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Outer Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -460,22 +470,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.69682</v>
+        <v>16.79711</v>
       </c>
       <c r="D2" t="n">
-        <v>16.38901</v>
+        <v>16.36993</v>
       </c>
       <c r="E2" t="n">
-        <v>17.00895</v>
+        <v>16.50587</v>
       </c>
       <c r="F2" t="n">
-        <v>41.80391</v>
+        <v>55.75981</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05026</v>
+        <v>43.24663</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83378</v>
+        <v>86.68828999999999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.05074</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.80167</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +501,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.74048</v>
+        <v>16.87438</v>
       </c>
       <c r="D3" t="n">
-        <v>16.53674</v>
+        <v>16.51329</v>
       </c>
       <c r="E3" t="n">
-        <v>16.80396</v>
+        <v>16.72587</v>
       </c>
       <c r="F3" t="n">
-        <v>42.36234</v>
+        <v>54.87369</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05023</v>
+        <v>42.51364</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86055</v>
+        <v>83.85476</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.05061</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.82138</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +532,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.1687</v>
+        <v>16.75418</v>
       </c>
       <c r="D4" t="n">
-        <v>16.50521</v>
+        <v>16.65213</v>
       </c>
       <c r="E4" t="n">
-        <v>16.80629</v>
+        <v>16.75166</v>
       </c>
       <c r="F4" t="n">
-        <v>43.09086</v>
+        <v>55.5656</v>
       </c>
       <c r="G4" t="n">
-        <v>0.051</v>
+        <v>43.38525</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81849</v>
+        <v>85.96869</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.05015</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.82843</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +563,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.86615</v>
+        <v>16.81002</v>
       </c>
       <c r="D5" t="n">
-        <v>16.38422</v>
+        <v>16.55662</v>
       </c>
       <c r="E5" t="n">
-        <v>16.63234</v>
+        <v>16.62676</v>
       </c>
       <c r="F5" t="n">
-        <v>42.60125</v>
+        <v>56.40356</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05111</v>
+        <v>42.25827</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81635</v>
+        <v>85.42610000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.05014</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.81664</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +594,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.72548</v>
+        <v>16.592</v>
       </c>
       <c r="D6" t="n">
-        <v>16.84525</v>
+        <v>16.50233</v>
       </c>
       <c r="E6" t="n">
-        <v>16.82133</v>
+        <v>16.56194</v>
       </c>
       <c r="F6" t="n">
-        <v>43.29201</v>
+        <v>55.18005</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05</v>
+        <v>42.4776</v>
       </c>
       <c r="H6" t="n">
-        <v>1.81386</v>
+        <v>84.89944</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.05095</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.82231</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +625,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.63149</v>
+        <v>16.67853</v>
       </c>
       <c r="D7" t="n">
-        <v>16.73669</v>
+        <v>16.32816</v>
       </c>
       <c r="E7" t="n">
-        <v>16.9218</v>
+        <v>16.57144</v>
       </c>
       <c r="F7" t="n">
-        <v>42.93886</v>
+        <v>54.6695</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05092</v>
+        <v>41.41738</v>
       </c>
       <c r="H7" t="n">
-        <v>1.81616</v>
+        <v>85.38088999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.04989</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.86661</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +656,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.1249</v>
+        <v>16.68003</v>
       </c>
       <c r="D8" t="n">
-        <v>16.4878</v>
+        <v>16.42742</v>
       </c>
       <c r="E8" t="n">
-        <v>16.21701</v>
+        <v>16.59401</v>
       </c>
       <c r="F8" t="n">
-        <v>42.2699</v>
+        <v>54.90342</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05036</v>
+        <v>42.74464</v>
       </c>
       <c r="H8" t="n">
-        <v>1.81756</v>
+        <v>83.72557</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.05167</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.86107</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +687,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.60499</v>
+        <v>16.86547</v>
       </c>
       <c r="D9" t="n">
-        <v>16.70156</v>
+        <v>16.65442</v>
       </c>
       <c r="E9" t="n">
-        <v>16.99934</v>
+        <v>16.82843</v>
       </c>
       <c r="F9" t="n">
-        <v>41.77583</v>
+        <v>55.51501</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04977</v>
+        <v>42.7421</v>
       </c>
       <c r="H9" t="n">
-        <v>1.81808</v>
+        <v>84.14085</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.05193</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.82972</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +718,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.61123</v>
+        <v>16.71642</v>
       </c>
       <c r="D10" t="n">
-        <v>16.52306</v>
+        <v>16.40489</v>
       </c>
       <c r="E10" t="n">
-        <v>16.92101</v>
+        <v>16.54398</v>
       </c>
       <c r="F10" t="n">
-        <v>42.8072</v>
+        <v>55.44064</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05159</v>
+        <v>42.91518</v>
       </c>
       <c r="H10" t="n">
-        <v>1.80155</v>
+        <v>85.22657</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.05081</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.83313</v>
       </c>
     </row>
     <row r="11">
@@ -696,15 +760,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Outer Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -722,22 +796,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.88344</v>
+        <v>16.94904</v>
       </c>
       <c r="D12" t="n">
-        <v>16.63066</v>
+        <v>16.52877</v>
       </c>
       <c r="E12" t="n">
-        <v>16.89248</v>
+        <v>16.66901</v>
       </c>
       <c r="F12" t="n">
-        <v>43.16897</v>
+        <v>56.68957</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04978</v>
+        <v>43.56893</v>
       </c>
       <c r="H12" t="n">
-        <v>1.80691</v>
+        <v>85.15264999999999</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.05041</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.82502</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +827,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.6826</v>
+        <v>16.79834</v>
       </c>
       <c r="D13" t="n">
-        <v>16.4639</v>
+        <v>16.6995</v>
       </c>
       <c r="E13" t="n">
-        <v>16.43133</v>
+        <v>16.798</v>
       </c>
       <c r="F13" t="n">
-        <v>41.49424</v>
+        <v>55.35641</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05149</v>
+        <v>42.31576</v>
       </c>
       <c r="H13" t="n">
-        <v>1.84757</v>
+        <v>82.566</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.0508</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.82789</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +858,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.54952</v>
+        <v>16.98459</v>
       </c>
       <c r="D14" t="n">
-        <v>16.70582</v>
+        <v>16.53034</v>
       </c>
       <c r="E14" t="n">
-        <v>16.33549</v>
+        <v>16.70914</v>
       </c>
       <c r="F14" t="n">
-        <v>41.98748</v>
+        <v>55.41462</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0502</v>
+        <v>42.25006</v>
       </c>
       <c r="H14" t="n">
-        <v>1.82863</v>
+        <v>86.88601</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.05097</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.82715</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +889,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.59255</v>
+        <v>16.873</v>
       </c>
       <c r="D15" t="n">
-        <v>16.63056</v>
+        <v>16.5159</v>
       </c>
       <c r="E15" t="n">
-        <v>17.09826</v>
+        <v>16.70528</v>
       </c>
       <c r="F15" t="n">
-        <v>42.75819</v>
+        <v>54.71181</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0505</v>
+        <v>42.70664</v>
       </c>
       <c r="H15" t="n">
-        <v>1.82536</v>
+        <v>86.59781</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.04951</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.82678</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +920,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.50453</v>
+        <v>17.03213</v>
       </c>
       <c r="D16" t="n">
-        <v>16.21208</v>
+        <v>16.61943</v>
       </c>
       <c r="E16" t="n">
-        <v>16.7089</v>
+        <v>16.6599</v>
       </c>
       <c r="F16" t="n">
-        <v>42.74747</v>
+        <v>54.74727</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05139</v>
+        <v>43.03162</v>
       </c>
       <c r="H16" t="n">
-        <v>1.82293</v>
+        <v>86.74014</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.05084</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.8213</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +951,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.45349</v>
+        <v>17.17985</v>
       </c>
       <c r="D17" t="n">
-        <v>16.55288</v>
+        <v>16.74745</v>
       </c>
       <c r="E17" t="n">
-        <v>16.76629</v>
+        <v>16.8781</v>
       </c>
       <c r="F17" t="n">
-        <v>42.85358</v>
+        <v>56.72246</v>
       </c>
       <c r="G17" t="n">
-        <v>0.04998</v>
+        <v>42.73238</v>
       </c>
       <c r="H17" t="n">
-        <v>1.80079</v>
+        <v>86.73175999999999</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.05043</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.83284</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +982,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.89321</v>
+        <v>16.66864</v>
       </c>
       <c r="D18" t="n">
-        <v>16.87923</v>
+        <v>16.63581</v>
       </c>
       <c r="E18" t="n">
-        <v>16.74014</v>
+        <v>16.64415</v>
       </c>
       <c r="F18" t="n">
-        <v>42.68203</v>
+        <v>55.97158</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05044</v>
+        <v>42.73852</v>
       </c>
       <c r="H18" t="n">
-        <v>1.80955</v>
+        <v>86.00431</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.05092</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.78546</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +1013,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.45238</v>
+        <v>17.0839</v>
       </c>
       <c r="D19" t="n">
-        <v>16.64839</v>
+        <v>16.52067</v>
       </c>
       <c r="E19" t="n">
-        <v>16.7864</v>
+        <v>16.7022</v>
       </c>
       <c r="F19" t="n">
-        <v>41.9416</v>
+        <v>55.30545</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05179</v>
+        <v>42.44872</v>
       </c>
       <c r="H19" t="n">
-        <v>1.82351</v>
+        <v>87.04339</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.05081</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.82938</v>
       </c>
     </row>
     <row r="20">
@@ -922,22 +1044,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.34554</v>
+        <v>16.92035</v>
       </c>
       <c r="D20" t="n">
-        <v>16.54897</v>
+        <v>16.39032</v>
       </c>
       <c r="E20" t="n">
-        <v>16.65498</v>
+        <v>16.86391</v>
       </c>
       <c r="F20" t="n">
-        <v>42.51805</v>
+        <v>55.92345</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05025</v>
+        <v>42.57069</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8375</v>
+        <v>84.78587</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.05058</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.83984</v>
       </c>
     </row>
     <row r="21">
@@ -958,7 +1086,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -970,20 +1103,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SR Pad 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.64067</v>
+        <v>16.77308</v>
       </c>
       <c r="D22" t="n">
-        <v>15.79431</v>
+        <v>15.79729</v>
       </c>
       <c r="E22" t="n">
-        <v>15.40559</v>
+        <v>16.53756</v>
       </c>
       <c r="F22" t="n">
-        <v>252.86295</v>
+        <v>21.65628</v>
+      </c>
+      <c r="G22" t="n">
+        <v>34.09528</v>
       </c>
     </row>
     <row r="23">
@@ -993,16 +1129,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.80686</v>
+        <v>16.74809</v>
       </c>
       <c r="D23" t="n">
-        <v>15.59381</v>
+        <v>15.87233</v>
       </c>
       <c r="E23" t="n">
-        <v>15.65051</v>
+        <v>16.5721</v>
       </c>
       <c r="F23" t="n">
-        <v>255.23562</v>
+        <v>21.67141</v>
+      </c>
+      <c r="G23" t="n">
+        <v>34.19267</v>
       </c>
     </row>
     <row r="24">
@@ -1012,16 +1151,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.65431</v>
+        <v>16.6506</v>
       </c>
       <c r="D24" t="n">
-        <v>15.29972</v>
+        <v>16.12055</v>
       </c>
       <c r="E24" t="n">
-        <v>15.63879</v>
+        <v>16.23366</v>
       </c>
       <c r="F24" t="n">
-        <v>256.74106</v>
+        <v>21.42288</v>
+      </c>
+      <c r="G24" t="n">
+        <v>33.91284</v>
       </c>
     </row>
     <row r="25">
@@ -1031,16 +1173,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.94578</v>
+        <v>16.5562</v>
       </c>
       <c r="D25" t="n">
-        <v>15.28797</v>
+        <v>16.09287</v>
       </c>
       <c r="E25" t="n">
-        <v>15.62807</v>
+        <v>16.23358</v>
       </c>
       <c r="F25" t="n">
-        <v>253.71195</v>
+        <v>21.7449</v>
+      </c>
+      <c r="G25" t="n">
+        <v>34.51776</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1195,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15.52571</v>
+        <v>16.59292</v>
       </c>
       <c r="D26" t="n">
-        <v>15.69733</v>
+        <v>16.06312</v>
       </c>
       <c r="E26" t="n">
-        <v>15.74556</v>
+        <v>16.16034</v>
       </c>
       <c r="F26" t="n">
-        <v>257.81241</v>
+        <v>21.79241</v>
+      </c>
+      <c r="G26" t="n">
+        <v>33.53692</v>
       </c>
     </row>
     <row r="27">
@@ -1069,16 +1217,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>15.5245</v>
+        <v>16.72287</v>
       </c>
       <c r="D27" t="n">
-        <v>15.71562</v>
+        <v>15.95792</v>
       </c>
       <c r="E27" t="n">
-        <v>15.73488</v>
+        <v>16.6233</v>
       </c>
       <c r="F27" t="n">
-        <v>252.04421</v>
+        <v>22.11173</v>
+      </c>
+      <c r="G27" t="n">
+        <v>33.63963</v>
       </c>
     </row>
     <row r="28">
@@ -1088,16 +1239,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>15.51297</v>
+        <v>16.65425</v>
       </c>
       <c r="D28" t="n">
-        <v>15.71758</v>
+        <v>16.19787</v>
       </c>
       <c r="E28" t="n">
-        <v>15.81637</v>
+        <v>16.5921</v>
       </c>
       <c r="F28" t="n">
-        <v>253.57674</v>
+        <v>21.67282</v>
+      </c>
+      <c r="G28" t="n">
+        <v>34.04033</v>
       </c>
     </row>
     <row r="29">
@@ -1107,16 +1261,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>15.88381</v>
+        <v>16.78843</v>
       </c>
       <c r="D29" t="n">
-        <v>15.44423</v>
+        <v>16.00412</v>
       </c>
       <c r="E29" t="n">
-        <v>15.42594</v>
+        <v>16.46125</v>
       </c>
       <c r="F29" t="n">
-        <v>254.70785</v>
+        <v>22.19611</v>
+      </c>
+      <c r="G29" t="n">
+        <v>34.29655</v>
       </c>
     </row>
     <row r="30">
@@ -1126,42 +1283,60 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15.82181</v>
+        <v>16.81532</v>
       </c>
       <c r="D30" t="n">
-        <v>15.34711</v>
+        <v>15.94076</v>
       </c>
       <c r="E30" t="n">
-        <v>15.88677</v>
+        <v>16.38898</v>
       </c>
       <c r="F30" t="n">
-        <v>254.57158</v>
+        <v>21.73433</v>
+      </c>
+      <c r="G30" t="n">
+        <v>33.88831</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Rz max</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
+          <t>Rz mean</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mean Stepheight</t>
+          <t>Rz min</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Rz max</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ra max</t>
         </is>
       </c>
     </row>
@@ -1173,23 +1348,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>roughness</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16.58514</v>
+        <v>0.7329</v>
       </c>
       <c r="D32" t="n">
-        <v>16.17133</v>
+        <v>0.08093</v>
       </c>
       <c r="E32" t="n">
-        <v>16.72981</v>
+        <v>0.61206</v>
       </c>
       <c r="F32" t="n">
-        <v>22.32116</v>
+        <v>0.95755</v>
       </c>
       <c r="G32" t="n">
-        <v>34.31562</v>
+        <v>0.10804</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09224</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.12754</v>
       </c>
     </row>
     <row r="33">
@@ -1199,19 +1383,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>16.69078</v>
+        <v>0.74266</v>
       </c>
       <c r="D33" t="n">
-        <v>15.764</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>16.59953</v>
+        <v>0.59933</v>
       </c>
       <c r="F33" t="n">
-        <v>21.72375</v>
+        <v>0.97052</v>
       </c>
       <c r="G33" t="n">
-        <v>34.53013</v>
+        <v>0.10847</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09241000000000001</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.12714</v>
       </c>
     </row>
     <row r="34">
@@ -1221,19 +1414,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>16.88993</v>
+        <v>0.73738</v>
       </c>
       <c r="D34" t="n">
-        <v>16.23243</v>
+        <v>0.08111</v>
       </c>
       <c r="E34" t="n">
-        <v>16.62857</v>
+        <v>0.60432</v>
       </c>
       <c r="F34" t="n">
-        <v>22.07249</v>
+        <v>0.96641</v>
       </c>
       <c r="G34" t="n">
-        <v>35.30886</v>
+        <v>0.11113</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00767</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09365999999999999</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.12659</v>
       </c>
     </row>
     <row r="35">
@@ -1243,19 +1445,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>16.84942</v>
+        <v>0.74296</v>
       </c>
       <c r="D35" t="n">
-        <v>16.20713</v>
+        <v>0.07997</v>
       </c>
       <c r="E35" t="n">
-        <v>16.3473</v>
+        <v>0.6138400000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>21.76824</v>
+        <v>0.97418</v>
       </c>
       <c r="G35" t="n">
-        <v>34.03259</v>
+        <v>0.10958</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00755</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.09284000000000001</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.12621</v>
       </c>
     </row>
     <row r="36">
@@ -1265,19 +1476,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>16.64942</v>
+        <v>0.7448399999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>16.23611</v>
+        <v>0.08035</v>
       </c>
       <c r="E36" t="n">
-        <v>16.15319</v>
+        <v>0.59976</v>
       </c>
       <c r="F36" t="n">
-        <v>21.88843</v>
+        <v>0.95484</v>
       </c>
       <c r="G36" t="n">
-        <v>33.82493</v>
+        <v>0.10827</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09179</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12794</v>
       </c>
     </row>
     <row r="37">
@@ -1287,19 +1507,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16.9756</v>
+        <v>0.761</v>
       </c>
       <c r="D37" t="n">
-        <v>16.06294</v>
+        <v>0.07892</v>
       </c>
       <c r="E37" t="n">
-        <v>16.33606</v>
+        <v>0.59557</v>
       </c>
       <c r="F37" t="n">
-        <v>21.98856</v>
+        <v>0.95595</v>
       </c>
       <c r="G37" t="n">
-        <v>34.76005</v>
+        <v>0.10856</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09136</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12652</v>
       </c>
     </row>
     <row r="38">
@@ -1309,19 +1538,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>16.13255</v>
+        <v>0.74583</v>
       </c>
       <c r="D38" t="n">
-        <v>15.98629</v>
+        <v>0.08048</v>
       </c>
       <c r="E38" t="n">
-        <v>16.4195</v>
+        <v>0.62307</v>
       </c>
       <c r="F38" t="n">
-        <v>21.97208</v>
+        <v>0.97301</v>
       </c>
       <c r="G38" t="n">
-        <v>34.47606</v>
+        <v>0.10853</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00749</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.09504</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.12683</v>
       </c>
     </row>
     <row r="39">
@@ -1331,19 +1569,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>16.71124</v>
+        <v>0.76364</v>
       </c>
       <c r="D39" t="n">
-        <v>15.86103</v>
+        <v>0.08083</v>
       </c>
       <c r="E39" t="n">
-        <v>16.51168</v>
+        <v>0.60189</v>
       </c>
       <c r="F39" t="n">
-        <v>21.91499</v>
+        <v>0.92954</v>
       </c>
       <c r="G39" t="n">
-        <v>33.8812</v>
+        <v>0.11147</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09404</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.12884</v>
       </c>
     </row>
     <row r="40">
@@ -1353,843 +1600,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>17.02808</v>
+        <v>0.7474499999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>15.86012</v>
+        <v>0.08134</v>
       </c>
       <c r="E40" t="n">
-        <v>16.15572</v>
+        <v>0.60511</v>
       </c>
       <c r="F40" t="n">
-        <v>22.04837</v>
+        <v>0.95521</v>
       </c>
       <c r="G40" t="n">
-        <v>33.70536</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Trace 2</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>17.12821</v>
-      </c>
-      <c r="D42" t="n">
-        <v>15.76178</v>
-      </c>
-      <c r="E42" t="n">
-        <v>16.65939</v>
-      </c>
-      <c r="F42" t="n">
-        <v>21.62717</v>
-      </c>
-      <c r="G42" t="n">
-        <v>35.12164</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>16.28699</v>
-      </c>
-      <c r="D43" t="n">
-        <v>16.01018</v>
-      </c>
-      <c r="E43" t="n">
-        <v>16.56698</v>
-      </c>
-      <c r="F43" t="n">
-        <v>21.89024</v>
-      </c>
-      <c r="G43" t="n">
-        <v>34.10439</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>16.54144</v>
-      </c>
-      <c r="D44" t="n">
-        <v>15.72974</v>
-      </c>
-      <c r="E44" t="n">
-        <v>15.9634</v>
-      </c>
-      <c r="F44" t="n">
-        <v>21.85326</v>
-      </c>
-      <c r="G44" t="n">
-        <v>34.12311</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>16.84678</v>
-      </c>
-      <c r="D45" t="n">
-        <v>15.91997</v>
-      </c>
-      <c r="E45" t="n">
-        <v>16.64874</v>
-      </c>
-      <c r="F45" t="n">
-        <v>21.17263</v>
-      </c>
-      <c r="G45" t="n">
-        <v>34.96005</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>16.89421</v>
-      </c>
-      <c r="D46" t="n">
-        <v>15.7152</v>
-      </c>
-      <c r="E46" t="n">
-        <v>16.5135</v>
-      </c>
-      <c r="F46" t="n">
-        <v>21.61557</v>
-      </c>
-      <c r="G46" t="n">
-        <v>33.76207</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>16.7293</v>
-      </c>
-      <c r="D47" t="n">
-        <v>15.93313</v>
-      </c>
-      <c r="E47" t="n">
-        <v>16.41251</v>
-      </c>
-      <c r="F47" t="n">
-        <v>22.05119</v>
-      </c>
-      <c r="G47" t="n">
-        <v>34.39181</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>16.99807</v>
-      </c>
-      <c r="D48" t="n">
-        <v>15.90449</v>
-      </c>
-      <c r="E48" t="n">
-        <v>16.20554</v>
-      </c>
-      <c r="F48" t="n">
-        <v>21.73195</v>
-      </c>
-      <c r="G48" t="n">
-        <v>34.83637</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>17.04923</v>
-      </c>
-      <c r="D49" t="n">
-        <v>16.03284</v>
-      </c>
-      <c r="E49" t="n">
-        <v>16.30177</v>
-      </c>
-      <c r="F49" t="n">
-        <v>21.7915</v>
-      </c>
-      <c r="G49" t="n">
-        <v>34.07279</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>16.94549</v>
-      </c>
-      <c r="D50" t="n">
-        <v>16.15503</v>
-      </c>
-      <c r="E50" t="n">
-        <v>16.49968</v>
-      </c>
-      <c r="F50" t="n">
-        <v>21.34853</v>
-      </c>
-      <c r="G50" t="n">
-        <v>34.45104</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.59557</v>
-      </c>
-      <c r="D52" t="n">
-        <v>1.09685</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0.61447</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1.11602</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0.60967</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1.12587</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>0.60009</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1.11717</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>0.60732</v>
-      </c>
-      <c r="D56" t="n">
-        <v>1.10753</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>0.60433</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1.10296</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>0.6116200000000001</v>
-      </c>
-      <c r="D58" t="n">
-        <v>1.14001</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>0.6111</v>
-      </c>
-      <c r="D59" t="n">
-        <v>1.11912</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>0.60636</v>
-      </c>
-      <c r="D60" t="n">
-        <v>1.10719</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>via 2</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>0.60568</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1.11648</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>0.61617</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1.11015</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>0.61312</v>
-      </c>
-      <c r="D64" t="n">
-        <v>1.1105</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>0.60812</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1.1081</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>0.61703</v>
-      </c>
-      <c r="D66" t="n">
-        <v>1.08609</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>0.60148</v>
-      </c>
-      <c r="D67" t="n">
-        <v>1.09716</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>0.60203</v>
-      </c>
-      <c r="D68" t="n">
-        <v>1.12588</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>0.60775</v>
-      </c>
-      <c r="D69" t="n">
-        <v>1.09636</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>0.60599</v>
-      </c>
-      <c r="D70" t="n">
-        <v>1.09751</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>roughness</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>0.73867</v>
-      </c>
-      <c r="D72" t="n">
-        <v>0.08033</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0.59829</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0.96536</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0.10671</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0.0074</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0.09443</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0.12671</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>0.74824</v>
-      </c>
-      <c r="D73" t="n">
-        <v>0.08049000000000001</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0.61099</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0.97986</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0.10867</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0.00759</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0.09352000000000001</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0.12804</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="D74" t="n">
-        <v>0.0819</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0.61367</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0.95389</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0.11074</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0.00755</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0.09657</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0.1251</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>0.74974</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0.08121</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0.61389</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0.9645</v>
-      </c>
-      <c r="G75" t="n">
-        <v>0.10986</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0.00753</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0.09211</v>
-      </c>
-      <c r="J75" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>0.74777</v>
-      </c>
-      <c r="D76" t="n">
-        <v>0.08118</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0.62415</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0.97748</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0.11121</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0.00742</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0.09303</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0.12554</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>0.73354</v>
-      </c>
-      <c r="D77" t="n">
-        <v>0.08209</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0.61339</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0.97604</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0.11107</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0.00759</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0.09349</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0.12496</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>0.75217</v>
-      </c>
-      <c r="D78" t="n">
-        <v>0.08139</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0.60277</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0.9636</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0.11009</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0.00774</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0.09159</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0.1258</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>0.75236</v>
-      </c>
-      <c r="D79" t="n">
-        <v>0.08037</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0.6026</v>
-      </c>
-      <c r="F79" t="n">
-        <v>0.9462699999999999</v>
-      </c>
-      <c r="G79" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0.09472</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0.12697</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>0.74758</v>
-      </c>
-      <c r="D80" t="n">
-        <v>0.08243</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0.60865</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.95874</v>
-      </c>
-      <c r="G80" t="n">
-        <v>0.10892</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0.00754</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0.09254</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0.12843</v>
+        <v>0.10825</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.09351</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.12537</v>
       </c>
     </row>
   </sheetData>
